--- a/data/trans_orig/Q02D_LAB-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q02D_LAB-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas diarias, de lunes a viernes, que dedica la persona entrevistada a cuidar a las personas del hogar que lo necesitan</t>
+          <t>Número medio de horas diarias, de lunes a viernes, que dedica la persona entrevistada a cuidar a las personas del hogar que lo necesitan (tasa de respuesta: 89,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,37 +716,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 10,22</t>
+          <t>4,43; 10,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,03; 6,17</t>
+          <t>4,11; 6,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,57</t>
+          <t>4,27; 7,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 11,64</t>
+          <t>2,0; 11,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 8,54</t>
+          <t>5,51; 8,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,21; 7,84</t>
+          <t>6,36; 7,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,45; 11,07</t>
+          <t>8,41; 11,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,57; 8,36</t>
+          <t>5,57; 8,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,79; 7,11</t>
+          <t>5,83; 7,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,24; 9,51</t>
+          <t>7,35; 9,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,42; 4,79</t>
+          <t>3,4; 4,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 5,92</t>
+          <t>4,94; 5,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 8,38</t>
+          <t>6,48; 8,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,4; 12,4</t>
+          <t>6,37; 13,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,39; 7,79</t>
+          <t>6,46; 7,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 8,28</t>
+          <t>7,44; 8,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,64; 10,09</t>
+          <t>8,62; 10,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,62; 11,33</t>
+          <t>8,63; 11,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,55; 6,59</t>
+          <t>5,54; 6,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,67; 7,3</t>
+          <t>6,66; 7,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,06; 9,27</t>
+          <t>8,07; 9,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,45; 11,11</t>
+          <t>8,44; 10,93</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,79; 3,54</t>
+          <t>2,81; 3,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 4,93</t>
+          <t>4,27; 4,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,97; 7,2</t>
+          <t>5,93; 7,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,05; 7,35</t>
+          <t>5,06; 7,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,59; 5,67</t>
+          <t>4,63; 5,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,14; 6,78</t>
+          <t>6,12; 6,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 8,89</t>
+          <t>7,68; 8,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 8,51</t>
+          <t>6,93; 8,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,96; 4,64</t>
+          <t>3,91; 4,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 5,91</t>
+          <t>5,41; 5,89</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,03; 7,94</t>
+          <t>7,06; 7,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 7,76</t>
+          <t>6,32; 7,62</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 2,9</t>
+          <t>1,89; 2,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 4,27</t>
+          <t>3,39; 4,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,72; 6,39</t>
+          <t>4,69; 6,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,1</t>
+          <t>3,57; 6,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,01; 5,7</t>
+          <t>4,01; 5,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1166,32 +1166,32 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,37; 8,0</t>
+          <t>6,38; 8,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 7,09</t>
+          <t>4,98; 7,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 4,16</t>
+          <t>3,11; 4,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 4,92</t>
+          <t>4,26; 4,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,79; 7,01</t>
+          <t>5,78; 7,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,18</t>
+          <t>4,56; 6,17</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,58</t>
+          <t>2,99; 8,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,92</t>
+          <t>4,58; 6,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,2</t>
+          <t>3,09; 5,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,72</t>
+          <t>1,49; 3,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 6,74</t>
+          <t>3,94; 6,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,0; 6,71</t>
+          <t>5,01; 6,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,53; 11,75</t>
+          <t>7,37; 11,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,44; 8,48</t>
+          <t>4,36; 8,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,06; 6,46</t>
+          <t>4,08; 6,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,13; 6,51</t>
+          <t>5,05; 6,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 8,77</t>
+          <t>5,93; 8,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,66</t>
+          <t>3,23; 6,58</t>
         </is>
       </c>
     </row>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,31</t>
+          <t>4,3; 7,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,32; 9,41</t>
+          <t>4,49; 9,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,7; 11,32</t>
+          <t>4,48; 11,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1436,17 +1436,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,24</t>
+          <t>4,58; 8,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,51; 7,77</t>
+          <t>5,48; 7,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,57; 9,33</t>
+          <t>4,63; 9,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,82; 7,75</t>
+          <t>4,76; 7,72</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,54; 7,77</t>
+          <t>5,63; 7,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,35; 9,59</t>
+          <t>5,12; 8,81</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,86; 4,29</t>
+          <t>2,91; 4,28</t>
         </is>
       </c>
     </row>
@@ -1556,17 +1556,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,89; 14,37</t>
+          <t>5,84; 14,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,94</t>
+          <t>4,08; 8,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,65; 7,45</t>
+          <t>2,86; 8,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1576,42 +1576,42 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,99; 10,9</t>
+          <t>5,03; 10,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,26; 8,44</t>
+          <t>5,31; 8,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,74</t>
+          <t>6,16; 11,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,31</t>
+          <t>3,06; 7,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,82; 10,7</t>
+          <t>5,94; 10,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,2; 7,62</t>
+          <t>5,36; 7,81</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,85; 10,36</t>
+          <t>5,81; 10,27</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,23</t>
+          <t>1,91; 7,12</t>
         </is>
       </c>
     </row>
@@ -1696,27 +1696,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,34; 4,03</t>
+          <t>3,32; 4,0</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,51; 4,97</t>
+          <t>4,49; 4,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,88; 6,67</t>
+          <t>5,9; 6,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,07; 6,97</t>
+          <t>5,08; 6,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,5; 6,22</t>
+          <t>5,43; 6,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1726,32 +1726,32 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,09; 8,87</t>
+          <t>8,1; 8,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,06; 8,2</t>
+          <t>7,02; 8,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,71; 5,24</t>
+          <t>4,73; 5,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,7; 6,02</t>
+          <t>5,7; 6,01</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,3; 7,85</t>
+          <t>7,31; 7,89</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,44; 7,52</t>
+          <t>6,45; 7,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q02D_LAB-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q02D_LAB-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,76</t>
+          <t>4,19</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,82</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,43</t>
+          <t>5,51</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 10,07</t>
+          <t>4,51; 10,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,12</t>
+          <t>4,15; 6,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,64</t>
+          <t>4,29; 7,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 11,75</t>
+          <t>2,0; 11,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,51; 8,64</t>
+          <t>5,53; 8,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 7,95</t>
+          <t>6,32; 7,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,41; 11,29</t>
+          <t>8,51; 11,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 10,63</t>
+          <t>3,67; 10,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,57; 8,45</t>
+          <t>5,67; 8,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,18</t>
+          <t>5,82; 7,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,35; 9,59</t>
+          <t>7,35; 9,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 9,06</t>
+          <t>3,66; 8,43</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,84</t>
+          <t>8,98</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,77</t>
+          <t>9,74</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,53</t>
+          <t>9,52</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 4,73</t>
+          <t>3,43; 4,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 5,91</t>
+          <t>4,93; 5,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,48; 8,47</t>
+          <t>6,51; 8,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,37; 13,15</t>
+          <t>6,67; 12,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,46; 7,87</t>
+          <t>6,48; 7,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,44; 8,24</t>
+          <t>7,49; 8,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,62; 10,09</t>
+          <t>8,61; 10,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,63; 11,31</t>
+          <t>8,73; 11,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 6,63</t>
+          <t>5,48; 6,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 7,29</t>
+          <t>6,64; 7,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,07; 9,24</t>
+          <t>8,0; 9,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,44; 10,93</t>
+          <t>8,39; 10,78</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,98</t>
+          <t>5,64</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,6</t>
+          <t>7,76</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,94</t>
+          <t>6,87</t>
         </is>
       </c>
     </row>
@@ -996,52 +996,52 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 3,56</t>
+          <t>2,8; 3,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 4,95</t>
+          <t>4,27; 4,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,93; 7,05</t>
+          <t>5,92; 7,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 7,51</t>
+          <t>4,8; 6,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 5,63</t>
+          <t>4,6; 5,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,12; 6,77</t>
+          <t>6,1; 6,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,68; 8,83</t>
+          <t>7,67; 8,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,93; 8,43</t>
+          <t>7,07; 8,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,91; 4,67</t>
+          <t>3,94; 4,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 5,89</t>
+          <t>5,46; 5,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,32; 7,62</t>
+          <t>6,33; 7,67</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,4</t>
+          <t>4,32</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,22</t>
+          <t>5,19</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 2,87</t>
+          <t>1,92; 2,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 4,27</t>
+          <t>3,39; 4,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,69; 6,46</t>
+          <t>4,75; 6,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,19</t>
+          <t>3,64; 5,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,01; 5,65</t>
+          <t>4,03; 5,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,77; 5,74</t>
+          <t>4,78; 5,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,38; 8,19</t>
+          <t>6,26; 7,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 7,07</t>
+          <t>5,07; 6,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 4,15</t>
+          <t>3,11; 4,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 4,91</t>
+          <t>4,25; 4,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,78; 7,02</t>
+          <t>5,81; 7,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 6,17</t>
+          <t>4,63; 6,17</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>3,72</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,17</t>
+          <t>5,97</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>4,93</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 8,57</t>
+          <t>2,95; 8,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,86</t>
+          <t>4,66; 7,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,12</t>
+          <t>3,11; 5,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,41</t>
+          <t>2,06; 5,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,94; 6,88</t>
+          <t>3,98; 6,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,01; 6,74</t>
+          <t>4,94; 6,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 11,51</t>
+          <t>7,62; 11,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,36; 8,26</t>
+          <t>4,31; 8,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,08; 6,45</t>
+          <t>4,0; 6,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,05; 6,6</t>
+          <t>5,04; 6,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,93; 8,62</t>
+          <t>5,85; 8,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,58</t>
+          <t>3,72; 6,51</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,67</t>
+          <t>3,6</t>
         </is>
       </c>
     </row>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,3; 7,43</t>
+          <t>4,2; 7,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,49; 9,71</t>
+          <t>4,61; 9,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,48; 11,44</t>
+          <t>4,56; 11,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,58; 8,45</t>
+          <t>4,61; 8,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,48; 7,65</t>
+          <t>5,48; 7,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,63; 9,56</t>
+          <t>4,73; 9,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 4,34</t>
+          <t>2,88; 4,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,76; 7,72</t>
+          <t>4,71; 7,85</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,63; 7,76</t>
+          <t>5,56; 7,73</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,12; 8,81</t>
+          <t>5,13; 8,98</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,91; 4,28</t>
+          <t>2,95; 4,14</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,44</t>
+          <t>5,35</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,2</t>
+          <t>4,09</t>
         </is>
       </c>
     </row>
@@ -1556,17 +1556,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,84; 14,02</t>
+          <t>5,62; 14,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,18</t>
+          <t>4,05; 7,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,86; 8,0</t>
+          <t>2,61; 7,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1576,42 +1576,42 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,03; 10,41</t>
+          <t>4,87; 10,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,31; 8,36</t>
+          <t>5,31; 8,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,16; 11,53</t>
+          <t>6,2; 11,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,06; 7,84</t>
+          <t>3,06; 8,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,94; 10,69</t>
+          <t>5,81; 10,78</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,36; 7,81</t>
+          <t>5,28; 7,72</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,81; 10,27</t>
+          <t>5,74; 10,38</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,12</t>
+          <t>1,81; 6,83</t>
         </is>
       </c>
     </row>
@@ -1643,14 +1643,14 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>5,72</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>5,82</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>5,82</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>6,6</t>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,61</t>
+          <t>7,67</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,95</t>
+          <t>6,92</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,32; 4,0</t>
+          <t>3,35; 4,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,49; 4,94</t>
+          <t>4,5; 4,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,9; 6,7</t>
+          <t>5,89; 6,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,92</t>
+          <t>5,03; 6,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,43; 6,19</t>
+          <t>5,51; 6,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,4; 6,82</t>
+          <t>6,41; 6,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,1; 8,86</t>
+          <t>8,14; 8,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,02; 8,24</t>
+          <t>7,1; 8,3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,73; 5,25</t>
+          <t>4,72; 5,26</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,7; 6,01</t>
+          <t>5,7; 6,03</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,31; 7,89</t>
+          <t>7,29; 7,88</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,45; 7,49</t>
+          <t>6,47; 7,45</t>
         </is>
       </c>
     </row>
